--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="МУЛТИАРТ ЕООД" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="100">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -73,6 +76,54 @@
     <t>2026-05-09</t>
   </si>
   <si>
+    <t>2026-05-16</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>1131 София Бояна</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1903 София, О5 Царско село</t>
+  </si>
+  <si>
+    <t>1117 София Черни Връх</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1110 Петрич вход</t>
+  </si>
+  <si>
+    <t>1142 Пазарджик Север</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
     <t>СА3341ХТ</t>
   </si>
   <si>
@@ -91,6 +142,9 @@
     <t>СА6443СК</t>
   </si>
   <si>
+    <t>СВ5931КЕ</t>
+  </si>
+  <si>
     <t>78970154027720033</t>
   </si>
   <si>
@@ -109,43 +163,139 @@
     <t>78970154027720066</t>
   </si>
   <si>
+    <t>78970154027720074</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTER</t>
+    <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>09:59</t>
-  </si>
-  <si>
-    <t>11:27</t>
-  </si>
-  <si>
-    <t>20:44</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>08:43</t>
-  </si>
-  <si>
-    <t>09:02</t>
-  </si>
-  <si>
-    <t>18:02</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:44:00</t>
+  </si>
+  <si>
+    <t>13:24:00</t>
+  </si>
+  <si>
+    <t>20:35:00</t>
+  </si>
+  <si>
+    <t>09:58:00</t>
+  </si>
+  <si>
+    <t>11:26:00</t>
+  </si>
+  <si>
+    <t>20:44:00</t>
+  </si>
+  <si>
+    <t>08:49:00</t>
+  </si>
+  <si>
+    <t>08:38:00</t>
+  </si>
+  <si>
+    <t>09:01:00</t>
+  </si>
+  <si>
+    <t>18:02:00</t>
+  </si>
+  <si>
+    <t>09:20:00</t>
+  </si>
+  <si>
+    <t>12:40:00</t>
+  </si>
+  <si>
+    <t>14:09:00</t>
+  </si>
+  <si>
+    <t>09:23:00</t>
+  </si>
+  <si>
+    <t>17:58:00</t>
+  </si>
+  <si>
+    <t>11:23:00</t>
+  </si>
+  <si>
+    <t>16:20:00</t>
+  </si>
+  <si>
+    <t>12:46:00</t>
+  </si>
+  <si>
+    <t>14:16:00</t>
+  </si>
+  <si>
+    <t>16:27:00</t>
+  </si>
+  <si>
+    <t>3231279125 3231279125</t>
+  </si>
+  <si>
+    <t>3231327842 3231327842</t>
+  </si>
+  <si>
+    <t>3231469000 3231469000</t>
+  </si>
+  <si>
+    <t>3231496935 3231496935</t>
+  </si>
+  <si>
+    <t>3231498406 3231498406</t>
+  </si>
+  <si>
+    <t>3231512604 3231512604</t>
+  </si>
+  <si>
+    <t>3231595341 3231595341</t>
+  </si>
+  <si>
+    <t>3231650973 3231650973</t>
+  </si>
+  <si>
+    <t>3231651964 3231651964</t>
+  </si>
+  <si>
+    <t>3231641068 3231641068</t>
+  </si>
+  <si>
+    <t>3231965530 3231965530</t>
+  </si>
+  <si>
+    <t>3232191222 3232191222</t>
+  </si>
+  <si>
+    <t>3232242683 3232242683</t>
+  </si>
+  <si>
+    <t>3232287679 3232287679</t>
+  </si>
+  <si>
+    <t>3232383914 3232383914</t>
+  </si>
+  <si>
+    <t>3232520388 3232520388</t>
+  </si>
+  <si>
+    <t>3232525335 3232525335</t>
+  </si>
+  <si>
+    <t>3232575072 3232575072</t>
+  </si>
+  <si>
+    <t>3232572050 3232572050</t>
+  </si>
+  <si>
+    <t>3232576199 3232576199</t>
   </si>
   <si>
     <t>Общи литри по продукт / МУЛТИАРТ ЕООД</t>
@@ -569,24 +719,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -626,528 +778,1001 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1131</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F2">
         <v>41.92</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2">
         <v>1.67</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>70.01000000000001</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>75.45999999999999</v>
       </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+      <c r="L2" t="s">
+        <v>54</v>
       </c>
       <c r="M2">
-        <v>270398</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1902</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F3">
         <v>16.5</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3">
         <v>1.67</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>27.56</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.8</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>29.7</v>
       </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+      <c r="L3" t="s">
+        <v>55</v>
       </c>
       <c r="M3">
-        <v>78633</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1903</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F4">
         <v>48.78</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4">
         <v>2.05</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>100</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>2.05</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>100</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>123882</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>1131</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F5">
         <v>23.8</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5">
         <v>1.67</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>39.75</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.8</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>42.84</v>
       </c>
-      <c r="K5" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+      <c r="L5" t="s">
+        <v>57</v>
       </c>
       <c r="M5">
-        <v>274041</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>1902</v>
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F6">
         <v>38.98</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6">
         <v>1.67</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>65.09999999999999</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.8</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>70.16</v>
       </c>
-      <c r="K6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+      <c r="L6" t="s">
+        <v>58</v>
       </c>
       <c r="M6">
-        <v>80183</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>1902</v>
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F7">
         <v>14.76</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7">
         <v>1.67</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>24.65</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.8</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>26.57</v>
       </c>
-      <c r="K7" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="L7" t="s">
+        <v>59</v>
       </c>
       <c r="M7">
-        <v>166894</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
-        <v>1131</v>
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="F8">
         <v>53.6</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8">
         <v>1.47</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>78.79000000000001</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.54</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>82.54000000000001</v>
       </c>
-      <c r="K8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
+      <c r="L8" t="s">
+        <v>60</v>
       </c>
       <c r="M8">
-        <v>275689</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9">
-        <v>1117</v>
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F9">
         <v>56.09</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9">
         <v>1.66</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>93.11</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.79</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>100.4</v>
       </c>
-      <c r="K9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
+      <c r="L9" t="s">
+        <v>61</v>
       </c>
       <c r="M9">
-        <v>124080</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10">
-        <v>1131</v>
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F10">
         <v>26.36</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10">
         <v>1.66</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>43.76</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.79</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>47.18</v>
       </c>
-      <c r="K10" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" t="s">
+        <v>62</v>
       </c>
       <c r="M10">
-        <v>276355</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11">
-        <v>1902</v>
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F11">
         <v>18.28</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11">
         <v>1.66</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>30.34</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.79</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>32.72</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>168169</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="3" t="s">
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>28.04</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12">
+        <v>1.65</v>
+      </c>
+      <c r="I12" s="1">
+        <v>46.27</v>
+      </c>
+      <c r="J12">
+        <v>1.76</v>
+      </c>
+      <c r="K12" s="1">
+        <v>49.35</v>
+      </c>
+      <c r="L12" t="s">
+        <v>64</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13">
+        <v>46.95</v>
+      </c>
+      <c r="G13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13">
+        <v>1.64</v>
+      </c>
+      <c r="I13" s="1">
+        <v>77</v>
+      </c>
+      <c r="J13">
+        <v>1.77</v>
+      </c>
+      <c r="K13" s="1">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>65</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14">
+        <v>74.38</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14">
+        <v>1.64</v>
+      </c>
+      <c r="I14" s="1">
+        <v>121.98</v>
+      </c>
+      <c r="J14">
+        <v>1.75</v>
+      </c>
+      <c r="K14" s="1">
+        <v>130.16</v>
+      </c>
+      <c r="L14" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15">
+        <v>39.97</v>
+      </c>
+      <c r="G15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15">
+        <v>1.64</v>
+      </c>
+      <c r="I15" s="1">
+        <v>65.55</v>
+      </c>
+      <c r="J15">
+        <v>1.74</v>
+      </c>
+      <c r="K15" s="1">
+        <v>69.55</v>
+      </c>
+      <c r="L15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16">
+        <v>29.07</v>
+      </c>
+      <c r="G16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16">
+        <v>1.64</v>
+      </c>
+      <c r="I16" s="1">
+        <v>47.67</v>
+      </c>
+      <c r="J16">
+        <v>1.72</v>
+      </c>
+      <c r="K16" s="1">
+        <v>50</v>
+      </c>
+      <c r="L16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="4" t="s">
+      <c r="E17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17">
+        <v>44.51</v>
+      </c>
+      <c r="G17" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17">
+        <v>1.64</v>
+      </c>
+      <c r="I17" s="1">
+        <v>73</v>
+      </c>
+      <c r="J17">
+        <v>1.71</v>
+      </c>
+      <c r="K17" s="1">
+        <v>76.11</v>
+      </c>
+      <c r="L17" t="s">
+        <v>69</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="6">
-        <v>236.69</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="E18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18">
+        <v>54.19</v>
+      </c>
+      <c r="G18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18">
+        <v>1.64</v>
+      </c>
+      <c r="I18" s="1">
+        <v>88.87</v>
+      </c>
+      <c r="J18">
+        <v>1.73</v>
+      </c>
+      <c r="K18" s="1">
+        <v>93.75</v>
+      </c>
+      <c r="L18" t="s">
+        <v>70</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19">
+        <v>20.29</v>
+      </c>
+      <c r="G19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19">
+        <v>1.63</v>
+      </c>
+      <c r="I19" s="1">
+        <v>33.07</v>
+      </c>
+      <c r="J19">
+        <v>1.73</v>
+      </c>
+      <c r="K19" s="1">
+        <v>35.1</v>
+      </c>
+      <c r="L19" t="s">
+        <v>71</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20">
+        <v>75.58</v>
+      </c>
+      <c r="G20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20">
+        <v>1.63</v>
+      </c>
+      <c r="I20" s="1">
+        <v>123.2</v>
+      </c>
+      <c r="J20">
+        <v>1.72</v>
+      </c>
+      <c r="K20" s="1">
+        <v>130</v>
+      </c>
+      <c r="L20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21">
+        <v>23.26</v>
+      </c>
+      <c r="G21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21">
+        <v>1.63</v>
+      </c>
+      <c r="I21" s="1">
+        <v>37.91</v>
+      </c>
+      <c r="J21">
+        <v>1.72</v>
+      </c>
+      <c r="K21" s="1">
+        <v>40.01</v>
+      </c>
+      <c r="L21" t="s">
+        <v>73</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="7">
-        <v>1.6658</v>
-      </c>
-      <c r="E16" s="6">
-        <v>394.28</v>
-      </c>
-      <c r="F16" s="6">
-        <v>425.03</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="6">
+      <c r="F25" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="6">
+        <v>672.9299999999999</v>
+      </c>
+      <c r="C26" s="6">
+        <v>18</v>
+      </c>
+      <c r="D26" s="7">
+        <v>1.6477</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1108.8</v>
+      </c>
+      <c r="F26" s="6">
+        <v>1182.16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="6">
         <v>53.6</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C27" s="6">
         <v>1</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D27" s="7">
         <v>1.47</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E27" s="6">
         <v>78.79000000000001</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F27" s="6">
         <v>82.54000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="6">
+    <row r="28" spans="1:14">
+      <c r="A28" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="6">
         <v>48.78</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C28" s="6">
         <v>1</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D28" s="7">
         <v>2.05</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E28" s="6">
         <v>100</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F28" s="6">
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="9">
-        <v>339.07</v>
-      </c>
-      <c r="C19" s="9">
-        <v>10</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="9">
-        <v>573.0700000000001</v>
-      </c>
-      <c r="F19" s="9">
-        <v>607.5700000000001</v>
+    <row r="29" spans="1:14">
+      <c r="A29" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="9">
+        <v>775.3099999999999</v>
+      </c>
+      <c r="C29" s="9">
+        <v>20</v>
+      </c>
+      <c r="D29" s="7"/>
+      <c r="E29" s="9">
+        <v>1287.59</v>
+      </c>
+      <c r="F29" s="9">
+        <v>1364.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A24:F24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
@@ -349,7 +349,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -359,12 +359,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -414,17 +408,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="80">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -82,22 +91,28 @@
     <t>2026-06-25</t>
   </si>
   <si>
-    <t>София Младост</t>
-  </si>
-  <si>
-    <t>София Бояна</t>
-  </si>
-  <si>
-    <t>София Царско Село</t>
-  </si>
-  <si>
-    <t>София Сребърна</t>
-  </si>
-  <si>
-    <t>София Малинова Долина</t>
-  </si>
-  <si>
-    <t>София България</t>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1131 София Бояна</t>
+  </si>
+  <si>
+    <t>1903 София, О5 Царско село</t>
+  </si>
+  <si>
+    <t>1180 София Сребърна</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1160 София бул. България</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
   </si>
   <si>
     <t>СА7846ХР</t>
@@ -142,37 +157,85 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-01 15:23:36</t>
-  </si>
-  <si>
-    <t>2026-06-05 21:15:21</t>
-  </si>
-  <si>
-    <t>2026-06-08 15:37:17</t>
-  </si>
-  <si>
-    <t>2026-06-10 08:27:33</t>
-  </si>
-  <si>
-    <t>2026-06-12 17:13:41</t>
-  </si>
-  <si>
-    <t>2026-06-13 10:11:28</t>
-  </si>
-  <si>
-    <t>2026-06-16 19:54:21</t>
-  </si>
-  <si>
-    <t>2026-06-22 21:11:40</t>
-  </si>
-  <si>
-    <t>2026-06-23 16:34:13</t>
-  </si>
-  <si>
-    <t>2026-06-24 09:08:35</t>
-  </si>
-  <si>
-    <t>2026-06-25 05:43:15</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>15:21:00</t>
+  </si>
+  <si>
+    <t>21:14:00</t>
+  </si>
+  <si>
+    <t>15:36:00</t>
+  </si>
+  <si>
+    <t>08:26:00</t>
+  </si>
+  <si>
+    <t>17:13:00</t>
+  </si>
+  <si>
+    <t>10:10:00</t>
+  </si>
+  <si>
+    <t>19:53:00</t>
+  </si>
+  <si>
+    <t>21:11:00</t>
+  </si>
+  <si>
+    <t>16:33:00</t>
+  </si>
+  <si>
+    <t>09:08:00</t>
+  </si>
+  <si>
+    <t>05:42:00</t>
+  </si>
+  <si>
+    <t>06:06:00</t>
+  </si>
+  <si>
+    <t>09:06:00</t>
+  </si>
+  <si>
+    <t>3232716098 3232716098</t>
+  </si>
+  <si>
+    <t>3232909023 3232909023</t>
+  </si>
+  <si>
+    <t>3233043098 3233043098</t>
+  </si>
+  <si>
+    <t>3233135585 3233135585</t>
+  </si>
+  <si>
+    <t>3233243995 3233243995</t>
+  </si>
+  <si>
+    <t>3233273398 3233273398</t>
+  </si>
+  <si>
+    <t>3233436197 3233436197</t>
+  </si>
+  <si>
+    <t>3233732382 3233732382</t>
+  </si>
+  <si>
+    <t>3233762836 3233762836</t>
+  </si>
+  <si>
+    <t>3233797755 3233797755</t>
+  </si>
+  <si>
+    <t>3233833053 3233833053</t>
+  </si>
+  <si>
+    <t>3233935380 3233935380</t>
+  </si>
+  <si>
+    <t>3233899267 3233899267</t>
   </si>
   <si>
     <t>Общи литри по продукт / МУЛТИАРТ ЕООД</t>
@@ -590,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -599,14 +662,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -640,483 +706,679 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F2">
         <v>35.13</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2">
         <v>1.62</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>56.91</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.71</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>60.07</v>
       </c>
-      <c r="K2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F3">
         <v>20.46</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3">
         <v>1.59</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>32.53</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.68</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>34.37</v>
       </c>
-      <c r="K3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F4">
         <v>60.25</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4">
         <v>1.58</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>95.2</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.66</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>100.02</v>
       </c>
-      <c r="K4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F5">
         <v>31.37</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5">
         <v>1.56</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>48.94</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.65</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>51.76</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>40</v>
       </c>
       <c r="F6">
         <v>59.07</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6">
         <v>1.56</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>92.15000000000001</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.63</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>96.28</v>
       </c>
-      <c r="K6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F7">
         <v>18.1</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7">
         <v>1.56</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>28.24</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.62</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>29.32</v>
       </c>
-      <c r="K7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F8">
         <v>32.41</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8">
         <v>1.56</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>50.56</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.61</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>52.18</v>
       </c>
-      <c r="K8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F9">
         <v>44.2</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9">
         <v>1.48</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>65.42</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.52</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>67.18000000000001</v>
       </c>
-      <c r="K9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F10">
         <v>38.96</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10">
         <v>1.48</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>57.66</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.54</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>60</v>
       </c>
-      <c r="K10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F11">
         <v>52.98</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11">
         <v>1.42</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>75.23</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.51</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>80</v>
       </c>
-      <c r="K11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F12">
         <v>56.99</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12">
         <v>1.47</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>83.78</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.53</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>87.19</v>
       </c>
-      <c r="K12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>9</v>
+      <c r="L12" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13">
+        <v>36.82</v>
+      </c>
+      <c r="G13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13">
+        <v>1.45</v>
+      </c>
+      <c r="I13" s="1">
+        <v>53.39</v>
+      </c>
+      <c r="J13">
+        <v>1.53</v>
+      </c>
+      <c r="K13" s="1">
+        <v>56.33</v>
+      </c>
+      <c r="L13" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14">
+        <v>15.58</v>
+      </c>
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14">
+        <v>1.45</v>
+      </c>
+      <c r="I14" s="1">
+        <v>22.59</v>
+      </c>
+      <c r="J14">
+        <v>1.54</v>
+      </c>
+      <c r="K14" s="1">
+        <v>23.99</v>
+      </c>
+      <c r="L14" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="6">
-        <v>396.94</v>
-      </c>
-      <c r="C17" s="6">
+      <c r="A17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="7">
-        <v>1.5403</v>
-      </c>
-      <c r="E17" s="6">
-        <v>611.39</v>
-      </c>
-      <c r="F17" s="6">
-        <v>638.37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="6">
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="6">
+        <v>449.34</v>
+      </c>
+      <c r="C19" s="6">
+        <v>12</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1.5297</v>
+      </c>
+      <c r="E19" s="6">
+        <v>687.37</v>
+      </c>
+      <c r="F19" s="6">
+        <v>718.6900000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="6">
         <v>52.98</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C20" s="6">
         <v>1</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D20" s="7">
         <v>1.42</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E20" s="6">
         <v>75.23</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F20" s="6">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="9">
-        <v>449.92</v>
-      </c>
-      <c r="C19" s="9">
-        <v>11</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="9">
-        <v>686.62</v>
-      </c>
-      <c r="F19" s="9">
-        <v>718.37</v>
+    <row r="21" spans="1:6">
+      <c r="A21" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="9">
+        <v>502.32</v>
+      </c>
+      <c r="C21" s="9">
+        <v>13</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="9">
+        <v>762.6</v>
+      </c>
+      <c r="F21" s="9">
+        <v>798.6900000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="94">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -76,25 +82,58 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>София Бояна</t>
-  </si>
-  <si>
-    <t>Кулата Струма</t>
-  </si>
-  <si>
-    <t>Бургас езеро</t>
-  </si>
-  <si>
-    <t>София Младост</t>
-  </si>
-  <si>
-    <t>София Цар Борис ІІІ</t>
-  </si>
-  <si>
-    <t>София Черни връх</t>
-  </si>
-  <si>
-    <t>София Царско Село</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>1131 София Бояна</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1122 София Борис III</t>
+  </si>
+  <si>
+    <t>1117 София Черни Връх</t>
+  </si>
+  <si>
+    <t>1903 София, О5 Царско село</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
   </si>
   <si>
     <t>СВ8488ХА</t>
@@ -106,6 +145,9 @@
     <t>СА6443СК</t>
   </si>
   <si>
+    <t>СВ4351КТ</t>
+  </si>
+  <si>
     <t>78970154027720082</t>
   </si>
   <si>
@@ -115,40 +157,127 @@
     <t>78970154027720066</t>
   </si>
   <si>
+    <t>78970154027720058</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
-    <t>2026-07-01 17:29:04</t>
-  </si>
-  <si>
-    <t>2026-07-05 11:27:46</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:32:40</t>
-  </si>
-  <si>
-    <t>2026-07-08 09:11:20</t>
-  </si>
-  <si>
-    <t>2026-07-08 14:00:55</t>
-  </si>
-  <si>
-    <t>2026-07-09 17:03:30</t>
-  </si>
-  <si>
-    <t>2026-07-09 17:06:35</t>
-  </si>
-  <si>
-    <t>2026-07-13 19:52:21</t>
-  </si>
-  <si>
-    <t>2026-07-14 18:24:07</t>
-  </si>
-  <si>
-    <t>2026-07-15 08:40:08</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>17:28:00</t>
+  </si>
+  <si>
+    <t>11:28:00</t>
+  </si>
+  <si>
+    <t>11:32:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>09:08:00</t>
+  </si>
+  <si>
+    <t>17:10:00</t>
+  </si>
+  <si>
+    <t>17:07:00</t>
+  </si>
+  <si>
+    <t>19:51:00</t>
+  </si>
+  <si>
+    <t>18:17:00</t>
+  </si>
+  <si>
+    <t>08:40:00</t>
+  </si>
+  <si>
+    <t>10:46:00</t>
+  </si>
+  <si>
+    <t>09:52:00</t>
+  </si>
+  <si>
+    <t>19:10:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>10:11:00</t>
+  </si>
+  <si>
+    <t>10:45:00</t>
+  </si>
+  <si>
+    <t>13:29:00</t>
+  </si>
+  <si>
+    <t>06:51:00</t>
+  </si>
+  <si>
+    <t>3234151476 3234151476</t>
+  </si>
+  <si>
+    <t>3234349565 3234349565</t>
+  </si>
+  <si>
+    <t>3234389286 3234389286</t>
+  </si>
+  <si>
+    <t>3234470926 3234470926</t>
+  </si>
+  <si>
+    <t>3234468594 3234468594</t>
+  </si>
+  <si>
+    <t>3234536195 3234536195</t>
+  </si>
+  <si>
+    <t>3234538717 3234538717</t>
+  </si>
+  <si>
+    <t>3234741931 3234741931</t>
+  </si>
+  <si>
+    <t>3234764058 3234764058</t>
+  </si>
+  <si>
+    <t>3234831526 3234831526</t>
+  </si>
+  <si>
+    <t>3234885159 3234885159</t>
+  </si>
+  <si>
+    <t>3234993328 3234993328</t>
+  </si>
+  <si>
+    <t>3235056749 3235056749</t>
+  </si>
+  <si>
+    <t>3235187741 3235187741</t>
+  </si>
+  <si>
+    <t>3235336922 3235336922</t>
+  </si>
+  <si>
+    <t>3235368444 3235368444</t>
+  </si>
+  <si>
+    <t>3235436594 3235436594</t>
+  </si>
+  <si>
+    <t>3235490198 3235490198</t>
+  </si>
+  <si>
+    <t>3235462434 3235462434</t>
   </si>
   <si>
     <t>Общи литри по продукт / МУЛТИАРТ ЕООД</t>
@@ -566,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -575,15 +704,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -620,478 +751,940 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F2">
         <v>65.36</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2">
         <v>1.44</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>94.12</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.53</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>100</v>
       </c>
-      <c r="K2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F3">
         <v>33.61</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3">
         <v>1.45</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>48.73</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.56</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>52.43</v>
       </c>
-      <c r="K3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F4">
         <v>32.95</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4">
         <v>1.45</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>47.78</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.53</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>50.41</v>
       </c>
-      <c r="K4" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="L4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5">
+        <v>39.72</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>1.45</v>
+      </c>
+      <c r="I5" s="1">
+        <v>57.59</v>
+      </c>
+      <c r="J5">
+        <v>1.55</v>
+      </c>
+      <c r="K5" s="1">
+        <v>61.57</v>
+      </c>
+      <c r="L5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="F5">
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6">
         <v>61.93</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6">
         <v>1.45</v>
       </c>
-      <c r="H5">
+      <c r="I6" s="1">
         <v>89.8</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J6">
         <v>1.54</v>
       </c>
-      <c r="J5">
+      <c r="K6" s="1">
         <v>95.37</v>
       </c>
-      <c r="K5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6">
-        <v>39.72</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="L6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7">
+        <v>43.6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7">
         <v>1.45</v>
       </c>
-      <c r="H6">
-        <v>57.59</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="I7" s="1">
+        <v>63.22</v>
+      </c>
+      <c r="J7">
         <v>1.55</v>
       </c>
-      <c r="J6">
-        <v>61.57</v>
-      </c>
-      <c r="K6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="K7" s="1">
+        <v>67.58</v>
+      </c>
+      <c r="L7" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8">
+        <v>13.81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8">
+        <v>1.81</v>
+      </c>
+      <c r="I8" s="1">
+        <v>25</v>
+      </c>
+      <c r="J8">
+        <v>1.81</v>
+      </c>
+      <c r="K8" s="1">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7">
-        <v>13.81</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="H7">
-        <v>25</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="J7">
-        <v>25</v>
-      </c>
-      <c r="K7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8">
-        <v>43.6</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.45</v>
-      </c>
-      <c r="H8">
-        <v>63.22</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J8">
-        <v>67.58</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="C9" t="s">
         <v>41</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F9">
         <v>35.14</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9">
         <v>1.49</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>52.36</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.58</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>55.52</v>
       </c>
-      <c r="K9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="L9" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="F10">
         <v>10.86</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10">
         <v>1.84</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>19.98</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.84</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>19.98</v>
       </c>
-      <c r="K10" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="L10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F11">
         <v>65.14</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11">
         <v>1.53</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>99.66</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.58</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>102.92</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
         <v>44</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="3" t="s">
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12">
+        <v>21.34</v>
+      </c>
+      <c r="G12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12">
+        <v>1.54</v>
+      </c>
+      <c r="I12" s="1">
+        <v>32.86</v>
+      </c>
+      <c r="J12">
+        <v>1.64</v>
+      </c>
+      <c r="K12" s="1">
+        <v>35</v>
+      </c>
+      <c r="L12" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="4" t="s">
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13">
+        <v>16.16</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13">
+        <v>1.57</v>
+      </c>
+      <c r="I13" s="1">
+        <v>25.37</v>
+      </c>
+      <c r="J13">
+        <v>1.67</v>
+      </c>
+      <c r="K13" s="1">
+        <v>26.99</v>
+      </c>
+      <c r="L13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14">
+        <v>50.87</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14">
+        <v>1.57</v>
+      </c>
+      <c r="I14" s="1">
+        <v>79.87</v>
+      </c>
+      <c r="J14">
+        <v>1.71</v>
+      </c>
+      <c r="K14" s="1">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="L14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15">
+        <v>35.01</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15">
+        <v>1.63</v>
+      </c>
+      <c r="I15" s="1">
+        <v>57.07</v>
+      </c>
+      <c r="J15">
+        <v>1.7</v>
+      </c>
+      <c r="K15" s="1">
+        <v>59.52</v>
+      </c>
+      <c r="L15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16">
+        <v>11.42</v>
+      </c>
+      <c r="G16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16">
+        <v>1.66</v>
+      </c>
+      <c r="I16" s="1">
+        <v>18.96</v>
+      </c>
+      <c r="J16">
+        <v>1.75</v>
+      </c>
+      <c r="K16" s="1">
+        <v>19.98</v>
+      </c>
+      <c r="L16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17">
+        <v>73.3</v>
+      </c>
+      <c r="G17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17">
+        <v>1.66</v>
+      </c>
+      <c r="I17" s="1">
+        <v>121.68</v>
+      </c>
+      <c r="J17">
+        <v>1.76</v>
+      </c>
+      <c r="K17" s="1">
+        <v>129.01</v>
+      </c>
+      <c r="L17" t="s">
+        <v>66</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18">
+        <v>18.54</v>
+      </c>
+      <c r="G18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18">
+        <v>1.66</v>
+      </c>
+      <c r="I18" s="1">
+        <v>30.78</v>
+      </c>
+      <c r="J18">
+        <v>1.78</v>
+      </c>
+      <c r="K18" s="1">
+        <v>33</v>
+      </c>
+      <c r="L18" t="s">
+        <v>67</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19">
+        <v>60.82</v>
+      </c>
+      <c r="G19" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19">
+        <v>1.69</v>
+      </c>
+      <c r="I19" s="1">
+        <v>102.79</v>
+      </c>
+      <c r="J19">
+        <v>1.74</v>
+      </c>
+      <c r="K19" s="1">
+        <v>105.83</v>
+      </c>
+      <c r="L19" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20">
+        <v>59.89</v>
+      </c>
+      <c r="G20" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20">
+        <v>1.69</v>
+      </c>
+      <c r="I20" s="1">
+        <v>101.21</v>
+      </c>
+      <c r="J20">
+        <v>1.77</v>
+      </c>
+      <c r="K20" s="1">
+        <v>106.01</v>
+      </c>
+      <c r="L20" t="s">
+        <v>68</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="6">
+        <v>724.8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>17</v>
+      </c>
+      <c r="D25" s="7">
+        <v>1.5506</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1123.85</v>
+      </c>
+      <c r="F25" s="6">
+        <v>1188.13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="6">
-        <v>377.45</v>
-      </c>
-      <c r="C16" s="6">
-        <v>8</v>
-      </c>
-      <c r="D16" s="7">
-        <v>1.4658</v>
-      </c>
-      <c r="E16" s="6">
-        <v>553.26</v>
-      </c>
-      <c r="F16" s="6">
-        <v>585.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="6">
+      <c r="B26" s="6">
         <v>24.67</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C26" s="6">
         <v>2</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D26" s="7">
         <v>1.8233</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E26" s="6">
         <v>44.98</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F26" s="6">
         <v>44.98</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="9">
-        <v>402.12</v>
-      </c>
-      <c r="C18" s="9">
-        <v>10</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="9">
-        <v>598.24</v>
-      </c>
-      <c r="F18" s="9">
-        <v>630.78</v>
+    <row r="27" spans="1:14">
+      <c r="A27" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="9">
+        <v>749.47</v>
+      </c>
+      <c r="C27" s="9">
+        <v>19</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="9">
+        <v>1168.83</v>
+      </c>
+      <c r="F27" s="9">
+        <v>1233.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
@@ -304,7 +304,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1635,7 +1635,7 @@
         <v>17</v>
       </c>
       <c r="D25" s="7">
-        <v>1.5506</v>
+        <v>1.550566</v>
       </c>
       <c r="E25" s="6">
         <v>1123.85</v>
@@ -1655,7 +1655,7 @@
         <v>2</v>
       </c>
       <c r="D26" s="7">
-        <v>1.8233</v>
+        <v>1.823267</v>
       </c>
       <c r="E26" s="6">
         <v>44.98</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="95">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -695,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -708,13 +711,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -757,846 +760,906 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2">
-        <v>65.36</v>
+        <v>65.35899999999999</v>
       </c>
       <c r="G2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H2">
-        <v>1.44</v>
+        <v>1.399</v>
       </c>
       <c r="I2" s="1">
-        <v>94.12</v>
+        <v>1.439</v>
       </c>
       <c r="J2">
+        <v>94.05160100000001</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.53</v>
       </c>
-      <c r="K2" s="1">
-        <v>100</v>
-      </c>
-      <c r="L2" t="s">
-        <v>51</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="L2" s="1">
+        <v>99.99927</v>
+      </c>
+      <c r="M2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3">
+        <v>33.609</v>
+      </c>
+      <c r="G3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3">
+        <v>1.406</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.446</v>
+      </c>
+      <c r="J3">
+        <v>48.598614</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L3" s="1">
+        <v>52.43004</v>
+      </c>
+      <c r="M3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4">
+        <v>32.948</v>
+      </c>
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4">
+        <v>1.406</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.446</v>
+      </c>
+      <c r="J4">
+        <v>47.642808</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="L4" s="1">
+        <v>50.41044</v>
+      </c>
+      <c r="M4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
         <v>31</v>
       </c>
-      <c r="C3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3">
-        <v>33.61</v>
-      </c>
-      <c r="G3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3">
-        <v>1.45</v>
-      </c>
-      <c r="I3" s="1">
-        <v>48.73</v>
-      </c>
-      <c r="J3">
-        <v>1.56</v>
-      </c>
-      <c r="K3" s="1">
-        <v>52.43</v>
-      </c>
-      <c r="L3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5">
+        <v>39.716</v>
+      </c>
+      <c r="G5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5">
+        <v>1.412</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.452</v>
+      </c>
+      <c r="J5">
+        <v>57.667632</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L5" s="1">
+        <v>61.5598</v>
+      </c>
+      <c r="M5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6">
+        <v>61.929</v>
+      </c>
+      <c r="G6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6">
+        <v>1.412</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.452</v>
+      </c>
+      <c r="J6">
+        <v>89.920908</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L6" s="1">
+        <v>95.37066</v>
+      </c>
+      <c r="M6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
         <v>41</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D7" t="s">
         <v>45</v>
       </c>
-      <c r="E4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4">
-        <v>32.95</v>
-      </c>
-      <c r="G4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4">
-        <v>1.45</v>
-      </c>
-      <c r="I4" s="1">
-        <v>47.78</v>
-      </c>
-      <c r="J4">
-        <v>1.53</v>
-      </c>
-      <c r="K4" s="1">
-        <v>50.41</v>
-      </c>
-      <c r="L4" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5">
-        <v>39.72</v>
-      </c>
-      <c r="G5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5">
-        <v>1.45</v>
-      </c>
-      <c r="I5" s="1">
-        <v>57.59</v>
-      </c>
-      <c r="J5">
-        <v>1.55</v>
-      </c>
-      <c r="K5" s="1">
-        <v>61.57</v>
-      </c>
-      <c r="L5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6">
-        <v>61.93</v>
-      </c>
-      <c r="G6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6">
-        <v>1.45</v>
-      </c>
-      <c r="I6" s="1">
-        <v>89.8</v>
-      </c>
-      <c r="J6">
-        <v>1.54</v>
-      </c>
-      <c r="K6" s="1">
-        <v>95.37</v>
-      </c>
-      <c r="L6" t="s">
-        <v>55</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7">
         <v>43.6</v>
       </c>
       <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7">
+        <v>1.412</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.452</v>
+      </c>
+      <c r="J7">
+        <v>63.3072</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L7" s="1">
+        <v>67.58</v>
+      </c>
+      <c r="M7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
         <v>50</v>
       </c>
-      <c r="H7">
-        <v>1.45</v>
-      </c>
-      <c r="I7" s="1">
-        <v>63.22</v>
-      </c>
-      <c r="J7">
-        <v>1.55</v>
-      </c>
-      <c r="K7" s="1">
-        <v>67.58</v>
-      </c>
-      <c r="L7" t="s">
-        <v>56</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>49</v>
-      </c>
       <c r="F8">
-        <v>13.81</v>
+        <v>13.812</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H8">
         <v>1.81</v>
       </c>
       <c r="I8" s="1">
-        <v>25</v>
+        <v>1.81</v>
       </c>
       <c r="J8">
+        <v>24.99972</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.81</v>
       </c>
-      <c r="K8" s="1">
-        <v>25</v>
-      </c>
-      <c r="L8" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="L8" s="1">
+        <v>24.99972</v>
+      </c>
+      <c r="M8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9">
+        <v>35.139</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9">
+        <v>1.451</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.491</v>
+      </c>
+      <c r="J9">
+        <v>52.392249</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="L9" s="1">
+        <v>55.51962</v>
+      </c>
+      <c r="M9" t="s">
+        <v>59</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
         <v>41</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>45</v>
       </c>
-      <c r="E9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9">
-        <v>35.14</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="E10" t="s">
         <v>50</v>
       </c>
-      <c r="H9">
-        <v>1.49</v>
-      </c>
-      <c r="I9" s="1">
-        <v>52.36</v>
-      </c>
-      <c r="J9">
-        <v>1.58</v>
-      </c>
-      <c r="K9" s="1">
-        <v>55.52</v>
-      </c>
-      <c r="L9" t="s">
-        <v>58</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>49</v>
-      </c>
       <c r="F10">
-        <v>10.86</v>
+        <v>10.859</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H10">
         <v>1.84</v>
       </c>
       <c r="I10" s="1">
-        <v>19.98</v>
+        <v>1.84</v>
       </c>
       <c r="J10">
+        <v>19.98056</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.84</v>
       </c>
-      <c r="K10" s="1">
-        <v>19.98</v>
-      </c>
-      <c r="L10" t="s">
-        <v>59</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="L10" s="1">
+        <v>19.98056</v>
+      </c>
+      <c r="M10" t="s">
+        <v>60</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11">
+        <v>65.139</v>
+      </c>
+      <c r="G11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11">
+        <v>1.489</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.529</v>
+      </c>
+      <c r="J11">
+        <v>99.597531</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="L11" s="1">
+        <v>102.91962</v>
+      </c>
+      <c r="M11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12">
+        <v>21.341</v>
+      </c>
+      <c r="G12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12">
+        <v>1.499</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.539</v>
+      </c>
+      <c r="J12">
+        <v>32.843799</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="L12" s="1">
+        <v>34.99924</v>
+      </c>
+      <c r="M12" t="s">
+        <v>62</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13">
+        <v>16.156</v>
+      </c>
+      <c r="G13" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13">
+        <v>1.528</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1.568</v>
+      </c>
+      <c r="J13">
+        <v>25.332608</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1.67</v>
+      </c>
+      <c r="L13" s="1">
+        <v>26.98052</v>
+      </c>
+      <c r="M13" t="s">
+        <v>63</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14">
+        <v>50.871</v>
+      </c>
+      <c r="G14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14">
+        <v>1.528</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1.568</v>
+      </c>
+      <c r="J14">
+        <v>79.765728</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="L14" s="1">
+        <v>86.98941000000001</v>
+      </c>
+      <c r="M14" t="s">
+        <v>64</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15">
+        <v>35.012</v>
+      </c>
+      <c r="G15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15">
+        <v>1.588</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1.628</v>
+      </c>
+      <c r="J15">
+        <v>56.999536</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="L15" s="1">
+        <v>59.5204</v>
+      </c>
+      <c r="M15" t="s">
+        <v>65</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16">
+        <v>11.417</v>
+      </c>
+      <c r="G16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16">
+        <v>1.619</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1.659</v>
+      </c>
+      <c r="J16">
+        <v>18.940803</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L16" s="1">
+        <v>19.97975</v>
+      </c>
+      <c r="M16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
         <v>36</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17">
+        <v>73.301</v>
+      </c>
+      <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17">
+        <v>1.619</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1.659</v>
+      </c>
+      <c r="J17">
+        <v>121.606359</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="L17" s="1">
+        <v>129.00976</v>
+      </c>
+      <c r="M17" t="s">
+        <v>67</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18">
+        <v>18.539</v>
+      </c>
+      <c r="G18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18">
+        <v>1.619</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1.659</v>
+      </c>
+      <c r="J18">
+        <v>30.756201</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1.78</v>
+      </c>
+      <c r="L18" s="1">
+        <v>32.99942</v>
+      </c>
+      <c r="M18" t="s">
+        <v>68</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C19" t="s">
         <v>44</v>
       </c>
-      <c r="E11" t="s">
+      <c r="D19" t="s">
         <v>48</v>
       </c>
-      <c r="F11">
-        <v>65.14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11">
-        <v>1.53</v>
-      </c>
-      <c r="I11" s="1">
-        <v>99.66</v>
-      </c>
-      <c r="J11">
-        <v>1.58</v>
-      </c>
-      <c r="K11" s="1">
-        <v>102.92</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="E19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19">
+        <v>60.822</v>
+      </c>
+      <c r="G19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19">
+        <v>1.653</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1.693</v>
+      </c>
+      <c r="J19">
+        <v>102.971646</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="L19" s="1">
+        <v>105.83028</v>
+      </c>
+      <c r="M19" t="s">
         <v>60</v>
       </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12">
-        <v>21.34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12">
-        <v>1.54</v>
-      </c>
-      <c r="I12" s="1">
-        <v>32.86</v>
-      </c>
-      <c r="J12">
-        <v>1.64</v>
-      </c>
-      <c r="K12" s="1">
-        <v>35</v>
-      </c>
-      <c r="L12" t="s">
-        <v>61</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" t="s">
         <v>30</v>
       </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13">
-        <v>16.16</v>
-      </c>
-      <c r="G13" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13">
-        <v>1.57</v>
-      </c>
-      <c r="I13" s="1">
-        <v>25.37</v>
-      </c>
-      <c r="J13">
-        <v>1.67</v>
-      </c>
-      <c r="K13" s="1">
-        <v>26.99</v>
-      </c>
-      <c r="L13" t="s">
-        <v>62</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14">
-        <v>50.87</v>
-      </c>
-      <c r="G14" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14">
-        <v>1.57</v>
-      </c>
-      <c r="I14" s="1">
-        <v>79.87</v>
-      </c>
-      <c r="J14">
-        <v>1.71</v>
-      </c>
-      <c r="K14" s="1">
-        <v>86.98999999999999</v>
-      </c>
-      <c r="L14" t="s">
-        <v>63</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15">
-        <v>35.01</v>
-      </c>
-      <c r="G15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15">
-        <v>1.63</v>
-      </c>
-      <c r="I15" s="1">
-        <v>57.07</v>
-      </c>
-      <c r="J15">
-        <v>1.7</v>
-      </c>
-      <c r="K15" s="1">
-        <v>59.52</v>
-      </c>
-      <c r="L15" t="s">
-        <v>64</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16">
-        <v>11.42</v>
-      </c>
-      <c r="G16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16">
-        <v>1.66</v>
-      </c>
-      <c r="I16" s="1">
-        <v>18.96</v>
-      </c>
-      <c r="J16">
-        <v>1.75</v>
-      </c>
-      <c r="K16" s="1">
-        <v>19.98</v>
-      </c>
-      <c r="L16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17">
-        <v>73.3</v>
-      </c>
-      <c r="G17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17">
-        <v>1.66</v>
-      </c>
-      <c r="I17" s="1">
-        <v>121.68</v>
-      </c>
-      <c r="J17">
-        <v>1.76</v>
-      </c>
-      <c r="K17" s="1">
-        <v>129.01</v>
-      </c>
-      <c r="L17" t="s">
-        <v>66</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18">
-        <v>18.54</v>
-      </c>
-      <c r="G18" t="s">
-        <v>50</v>
-      </c>
-      <c r="H18">
-        <v>1.66</v>
-      </c>
-      <c r="I18" s="1">
-        <v>30.78</v>
-      </c>
-      <c r="J18">
-        <v>1.78</v>
-      </c>
-      <c r="K18" s="1">
-        <v>33</v>
-      </c>
-      <c r="L18" t="s">
-        <v>67</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>39</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>43</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>47</v>
       </c>
-      <c r="E19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19">
-        <v>60.82</v>
-      </c>
-      <c r="G19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19">
-        <v>1.69</v>
-      </c>
-      <c r="I19" s="1">
-        <v>102.79</v>
-      </c>
-      <c r="J19">
-        <v>1.74</v>
-      </c>
-      <c r="K19" s="1">
-        <v>105.83</v>
-      </c>
-      <c r="L19" t="s">
-        <v>59</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" t="s">
-        <v>46</v>
-      </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F20">
-        <v>59.89</v>
+        <v>59.893</v>
       </c>
       <c r="G20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H20">
-        <v>1.69</v>
+        <v>1.653</v>
       </c>
       <c r="I20" s="1">
-        <v>101.21</v>
+        <v>1.693</v>
       </c>
       <c r="J20">
+        <v>101.398849</v>
+      </c>
+      <c r="K20" s="1">
         <v>1.77</v>
       </c>
-      <c r="K20" s="1">
-        <v>106.01</v>
-      </c>
-      <c r="L20" t="s">
-        <v>68</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="L20" s="1">
+        <v>106.01061</v>
+      </c>
+      <c r="M20" t="s">
+        <v>69</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1604,58 +1667,58 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:15">
       <c r="A24" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" s="6">
-        <v>724.8</v>
+        <v>724.7910000000001</v>
       </c>
       <c r="C25" s="6">
         <v>17</v>
       </c>
       <c r="D25" s="7">
-        <v>1.550566</v>
+        <v>1.550508</v>
       </c>
       <c r="E25" s="6">
-        <v>1123.85</v>
+        <v>1123.79</v>
       </c>
       <c r="F25" s="6">
-        <v>1188.13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>1188.11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B26" s="6">
-        <v>24.67</v>
+        <v>24.671</v>
       </c>
       <c r="C26" s="6">
         <v>2</v>
       </c>
       <c r="D26" s="7">
-        <v>1.823267</v>
+        <v>1.823205</v>
       </c>
       <c r="E26" s="6">
         <v>44.98</v>
@@ -1664,22 +1727,22 @@
         <v>44.98</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:15">
       <c r="A27" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" s="9">
-        <v>749.47</v>
+        <v>749.462</v>
       </c>
       <c r="C27" s="9">
         <v>19</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="9">
-        <v>1168.83</v>
+        <v>1168.77</v>
       </c>
       <c r="F27" s="9">
-        <v>1233.11</v>
+        <v>1233.09</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МУЛТИАРТ ЕООД/МУЛТИАРТ ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="94">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -306,8 +303,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -400,10 +397,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -698,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -711,13 +708,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -760,906 +757,846 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F2">
         <v>65.35899999999999</v>
       </c>
       <c r="G2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <v>1.439</v>
+      </c>
+      <c r="I2" s="1">
+        <v>94.05200000000001</v>
+      </c>
+      <c r="J2">
+        <v>1.53</v>
+      </c>
+      <c r="K2" s="1">
+        <v>99.999</v>
+      </c>
+      <c r="L2" t="s">
         <v>51</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.439</v>
-      </c>
-      <c r="J2">
-        <v>94.05160100000001</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L2" s="1">
-        <v>99.99927</v>
-      </c>
-      <c r="M2" t="s">
-        <v>52</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F3">
         <v>33.609</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>1.406</v>
+        <v>1.446</v>
       </c>
       <c r="I3" s="1">
-        <v>1.446</v>
+        <v>48.599</v>
       </c>
       <c r="J3">
-        <v>48.598614</v>
+        <v>1.56</v>
       </c>
       <c r="K3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L3" s="1">
-        <v>52.43004</v>
-      </c>
-      <c r="M3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>52.43</v>
+      </c>
+      <c r="L3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F4">
         <v>32.948</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>1.406</v>
+        <v>1.446</v>
       </c>
       <c r="I4" s="1">
-        <v>1.446</v>
+        <v>47.643</v>
       </c>
       <c r="J4">
-        <v>47.642808</v>
+        <v>1.53</v>
       </c>
       <c r="K4" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L4" s="1">
-        <v>50.41044</v>
-      </c>
-      <c r="M4" t="s">
-        <v>54</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>50.41</v>
+      </c>
+      <c r="L4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5">
         <v>39.716</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>1.412</v>
+        <v>1.452</v>
       </c>
       <c r="I5" s="1">
-        <v>1.452</v>
+        <v>57.668</v>
       </c>
       <c r="J5">
-        <v>57.667632</v>
+        <v>1.55</v>
       </c>
       <c r="K5" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L5" s="1">
-        <v>61.5598</v>
-      </c>
-      <c r="M5" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>61.56</v>
+      </c>
+      <c r="L5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6">
         <v>61.929</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>1.412</v>
+        <v>1.452</v>
       </c>
       <c r="I6" s="1">
-        <v>1.452</v>
+        <v>89.92100000000001</v>
       </c>
       <c r="J6">
-        <v>89.920908</v>
+        <v>1.54</v>
       </c>
       <c r="K6" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L6" s="1">
-        <v>95.37066</v>
-      </c>
-      <c r="M6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>95.371</v>
+      </c>
+      <c r="L6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7">
         <v>43.6</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H7">
-        <v>1.412</v>
+        <v>1.452</v>
       </c>
       <c r="I7" s="1">
-        <v>1.452</v>
+        <v>63.307</v>
       </c>
       <c r="J7">
-        <v>63.3072</v>
+        <v>1.55</v>
       </c>
       <c r="K7" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L7" s="1">
         <v>67.58</v>
       </c>
-      <c r="M7" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="L7" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8">
         <v>13.812</v>
       </c>
       <c r="G8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H8">
         <v>1.81</v>
       </c>
       <c r="I8" s="1">
+        <v>25</v>
+      </c>
+      <c r="J8">
         <v>1.81</v>
       </c>
-      <c r="J8">
-        <v>24.99972</v>
-      </c>
       <c r="K8" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="L8" s="1">
-        <v>24.99972</v>
-      </c>
-      <c r="M8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9">
         <v>35.139</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H9">
-        <v>1.451</v>
+        <v>1.491</v>
       </c>
       <c r="I9" s="1">
-        <v>1.491</v>
+        <v>52.392</v>
       </c>
       <c r="J9">
-        <v>52.392249</v>
+        <v>1.58</v>
       </c>
       <c r="K9" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L9" s="1">
-        <v>55.51962</v>
-      </c>
-      <c r="M9" t="s">
-        <v>59</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>55.52</v>
+      </c>
+      <c r="L9" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F10">
         <v>10.859</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H10">
         <v>1.84</v>
       </c>
       <c r="I10" s="1">
+        <v>19.981</v>
+      </c>
+      <c r="J10">
         <v>1.84</v>
       </c>
-      <c r="J10">
-        <v>19.98056</v>
-      </c>
       <c r="K10" s="1">
-        <v>1.84</v>
-      </c>
-      <c r="L10" s="1">
-        <v>19.98056</v>
-      </c>
-      <c r="M10" t="s">
-        <v>60</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>19.981</v>
+      </c>
+      <c r="L10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11">
         <v>65.139</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H11">
-        <v>1.489</v>
+        <v>1.529</v>
       </c>
       <c r="I11" s="1">
-        <v>1.529</v>
+        <v>99.598</v>
       </c>
       <c r="J11">
-        <v>99.597531</v>
+        <v>1.58</v>
       </c>
       <c r="K11" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L11" s="1">
-        <v>102.91962</v>
-      </c>
-      <c r="M11" t="s">
-        <v>61</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>102.92</v>
+      </c>
+      <c r="L11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F12">
         <v>21.341</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H12">
-        <v>1.499</v>
+        <v>1.539</v>
       </c>
       <c r="I12" s="1">
-        <v>1.539</v>
+        <v>32.844</v>
       </c>
       <c r="J12">
-        <v>32.843799</v>
+        <v>1.64</v>
       </c>
       <c r="K12" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="L12" s="1">
-        <v>34.99924</v>
-      </c>
-      <c r="M12" t="s">
-        <v>62</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>34.999</v>
+      </c>
+      <c r="L12" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13">
         <v>16.156</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H13">
-        <v>1.528</v>
+        <v>1.568</v>
       </c>
       <c r="I13" s="1">
-        <v>1.568</v>
+        <v>25.333</v>
       </c>
       <c r="J13">
-        <v>25.332608</v>
+        <v>1.67</v>
       </c>
       <c r="K13" s="1">
-        <v>1.67</v>
-      </c>
-      <c r="L13" s="1">
-        <v>26.98052</v>
-      </c>
-      <c r="M13" t="s">
-        <v>63</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>26.981</v>
+      </c>
+      <c r="L13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F14">
         <v>50.871</v>
       </c>
       <c r="G14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H14">
-        <v>1.528</v>
+        <v>1.568</v>
       </c>
       <c r="I14" s="1">
-        <v>1.568</v>
+        <v>79.76600000000001</v>
       </c>
       <c r="J14">
-        <v>79.765728</v>
+        <v>1.71</v>
       </c>
       <c r="K14" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="L14" s="1">
-        <v>86.98941000000001</v>
-      </c>
-      <c r="M14" t="s">
-        <v>64</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>86.989</v>
+      </c>
+      <c r="L14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15">
         <v>35.012</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H15">
-        <v>1.588</v>
+        <v>1.628</v>
       </c>
       <c r="I15" s="1">
-        <v>1.628</v>
+        <v>57</v>
       </c>
       <c r="J15">
-        <v>56.999536</v>
+        <v>1.7</v>
       </c>
       <c r="K15" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L15" s="1">
-        <v>59.5204</v>
-      </c>
-      <c r="M15" t="s">
-        <v>65</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>59.52</v>
+      </c>
+      <c r="L15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16">
         <v>11.417</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H16">
-        <v>1.619</v>
+        <v>1.659</v>
       </c>
       <c r="I16" s="1">
-        <v>1.659</v>
+        <v>18.941</v>
       </c>
       <c r="J16">
-        <v>18.940803</v>
+        <v>1.75</v>
       </c>
       <c r="K16" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L16" s="1">
-        <v>19.97975</v>
-      </c>
-      <c r="M16" t="s">
-        <v>66</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>19.98</v>
+      </c>
+      <c r="L16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17">
         <v>73.301</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H17">
-        <v>1.619</v>
+        <v>1.659</v>
       </c>
       <c r="I17" s="1">
-        <v>1.659</v>
+        <v>121.606</v>
       </c>
       <c r="J17">
-        <v>121.606359</v>
+        <v>1.76</v>
       </c>
       <c r="K17" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L17" s="1">
-        <v>129.00976</v>
-      </c>
-      <c r="M17" t="s">
-        <v>67</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>129.01</v>
+      </c>
+      <c r="L17" t="s">
+        <v>66</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F18">
         <v>18.539</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H18">
-        <v>1.619</v>
+        <v>1.659</v>
       </c>
       <c r="I18" s="1">
-        <v>1.659</v>
+        <v>30.756</v>
       </c>
       <c r="J18">
-        <v>30.756201</v>
+        <v>1.78</v>
       </c>
       <c r="K18" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L18" s="1">
-        <v>32.99942</v>
-      </c>
-      <c r="M18" t="s">
-        <v>68</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>32.999</v>
+      </c>
+      <c r="L18" t="s">
+        <v>67</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F19">
         <v>60.822</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H19">
-        <v>1.653</v>
+        <v>1.693</v>
       </c>
       <c r="I19" s="1">
-        <v>1.693</v>
+        <v>102.972</v>
       </c>
       <c r="J19">
-        <v>102.971646</v>
+        <v>1.74</v>
       </c>
       <c r="K19" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L19" s="1">
-        <v>105.83028</v>
-      </c>
-      <c r="M19" t="s">
-        <v>60</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>105.83</v>
+      </c>
+      <c r="L19" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F20">
         <v>59.893</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H20">
-        <v>1.653</v>
+        <v>1.693</v>
       </c>
       <c r="I20" s="1">
-        <v>1.693</v>
+        <v>101.399</v>
       </c>
       <c r="J20">
-        <v>101.398849</v>
+        <v>1.77</v>
       </c>
       <c r="K20" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L20" s="1">
-        <v>106.01061</v>
-      </c>
-      <c r="M20" t="s">
-        <v>69</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
+        <v>106.011</v>
+      </c>
+      <c r="L20" t="s">
+        <v>68</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="3" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1667,69 +1604,69 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:14">
       <c r="A24" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="E24" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" s="6">
         <v>724.7910000000001</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="7">
         <v>17</v>
       </c>
       <c r="D25" s="7">
-        <v>1.550508</v>
-      </c>
-      <c r="E25" s="6">
-        <v>1123.79</v>
-      </c>
-      <c r="F25" s="6">
-        <v>1188.11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>1.551</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1123.797</v>
+      </c>
+      <c r="F25" s="7">
+        <v>1188.109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26" s="6">
         <v>24.671</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="7">
         <v>2</v>
       </c>
       <c r="D26" s="7">
-        <v>1.823205</v>
-      </c>
-      <c r="E26" s="6">
-        <v>44.98</v>
-      </c>
-      <c r="F26" s="6">
-        <v>44.98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>1.823</v>
+      </c>
+      <c r="E26" s="7">
+        <v>44.981</v>
+      </c>
+      <c r="F26" s="7">
+        <v>44.981</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B27" s="9">
         <v>749.462</v>
@@ -1739,7 +1676,7 @@
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="9">
-        <v>1168.77</v>
+        <v>1168.778</v>
       </c>
       <c r="F27" s="9">
         <v>1233.09</v>
